--- a/ksoft_old/docs/records/Stock_Group_Accounts.xlsx
+++ b/ksoft_old/docs/records/Stock_Group_Accounts.xlsx
@@ -40640,13 +40640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{031AF0AD-E098-47C1-A3E4-B51317FDDDBC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0FC4081-E129-4E9A-ADCB-8999BA92F5D2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A53DBB5-0053-43C0-AE78-8A3D8EE7F381}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A928845-D4B8-4DA3-8A05-A8EF84B2F200}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E99416-5C96-497E-8475-B19962645306}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E42227D-D697-4413-A48F-FA61DE4B7063}"/>
 </file>
--- a/ksoft_old/docs/records/Stock_Group_Accounts.xlsx
+++ b/ksoft_old/docs/records/Stock_Group_Accounts.xlsx
@@ -40640,13 +40640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0FC4081-E129-4E9A-ADCB-8999BA92F5D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0EC28BC-1CEC-4777-989C-6F29494D9531}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A928845-D4B8-4DA3-8A05-A8EF84B2F200}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE766ECA-12B9-4129-9610-FFF669C9BFF0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E42227D-D697-4413-A48F-FA61DE4B7063}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88195960-E38B-464A-AD87-443B803B7B55}"/>
 </file>
--- a/ksoft_old/docs/records/Stock_Group_Accounts.xlsx
+++ b/ksoft_old/docs/records/Stock_Group_Accounts.xlsx
@@ -40640,13 +40640,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0EC28BC-1CEC-4777-989C-6F29494D9531}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{031AF0AD-E098-47C1-A3E4-B51317FDDDBC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE766ECA-12B9-4129-9610-FFF669C9BFF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A53DBB5-0053-43C0-AE78-8A3D8EE7F381}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88195960-E38B-464A-AD87-443B803B7B55}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E99416-5C96-497E-8475-B19962645306}"/>
 </file>